--- a/artfynd/A 22235-2026 artfynd.xlsx
+++ b/artfynd/A 22235-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133749940</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133748350</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22235-2026 artfynd.xlsx
+++ b/artfynd/A 22235-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133749940</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133748350</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22235-2026 artfynd.xlsx
+++ b/artfynd/A 22235-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133749940</v>
+        <v>133748350</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -704,16 +704,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Frumossen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493629</v>
+        <v>493588</v>
       </c>
       <c r="R2" t="n">
-        <v>6672621</v>
+        <v>6672596</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,19 +760,19 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosöksspår på gran</t>
+          <t>Födosöksspår nedre del av gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133748350</v>
+        <v>133749940</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -816,21 +821,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Frumossen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493588</v>
+        <v>493629</v>
       </c>
       <c r="R3" t="n">
-        <v>6672596</v>
+        <v>6672621</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,19 +872,19 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosöksspår nedre del av gammal gran</t>
+          <t>Födosöksspår på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
